--- a/RobotOnTheFloor/01-ZigZagCrossRoted/01-Pwm-XYTheta/Ts-05/Resumo_Estatisticas.xlsx
+++ b/RobotOnTheFloor/01-ZigZagCrossRoted/01-Pwm-XYTheta/Ts-05/Resumo_Estatisticas.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.2324199875691499</v>
+        <v>-16.53007527089422</v>
       </c>
       <c r="D2" t="n">
-        <v>1.493777848734448</v>
+        <v>5.928079278763787</v>
       </c>
       <c r="E2" t="n">
-        <v>1.059373989861635</v>
+        <v>5.7446303018008</v>
       </c>
       <c r="F2" t="n">
-        <v>1.284034189271823</v>
+        <v>1.942639910554516</v>
       </c>
     </row>
     <row r="3">
@@ -497,16 +497,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1.431073369303658</v>
+        <v>-2.804472738095686</v>
       </c>
       <c r="D3" t="n">
-        <v>2.634330076850951</v>
+        <v>2.518671837597274</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5596071389167883</v>
+        <v>0.8757490131457725</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6063946633133749</v>
+        <v>0.5797713712407696</v>
       </c>
     </row>
     <row r="4">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.3019397573836626</v>
+        <v>-0.2060158142649251</v>
       </c>
       <c r="D4" t="n">
-        <v>1.620754069680083</v>
+        <v>1.380733324250744</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3077476518484005</v>
+        <v>0.2850735088372415</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3831077869302678</v>
+        <v>0.3263725805723174</v>
       </c>
     </row>
     <row r="5">
@@ -545,16 +545,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.3456255490595532</v>
+        <v>-3.247083740525556</v>
       </c>
       <c r="D5" t="n">
-        <v>1.319963864448013</v>
+        <v>2.652331742933204</v>
       </c>
       <c r="E5" t="n">
-        <v>1.157700534838912</v>
+        <v>1.397959311396207</v>
       </c>
       <c r="F5" t="n">
-        <v>1.135622664795192</v>
+        <v>0.8730347889223331</v>
       </c>
     </row>
     <row r="6">
@@ -569,16 +569,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-3.763535642103039</v>
+        <v>-1.316947062326302</v>
       </c>
       <c r="D6" t="n">
-        <v>2.981577685046018</v>
+        <v>2.334960612589897</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4653366249434904</v>
+        <v>0.2208829048923583</v>
       </c>
       <c r="F6" t="n">
-        <v>0.291262079515711</v>
+        <v>0.2226002014911216</v>
       </c>
     </row>
     <row r="7">
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-3.294921430258948</v>
+        <v>-0.1584791890435953</v>
       </c>
       <c r="D7" t="n">
-        <v>1.436036753470336</v>
+        <v>0.6004461892301372</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4485216242284979</v>
+        <v>0.1209807853163495</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1499663143033331</v>
+        <v>0.06270501205398672</v>
       </c>
     </row>
     <row r="8">
@@ -617,16 +617,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.57765463990725</v>
+        <v>-0.4016635319263483</v>
       </c>
       <c r="D8" t="n">
-        <v>1.588989899726131</v>
+        <v>0.3214646730448776</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2940625474650101</v>
+        <v>0.1152086465500066</v>
       </c>
       <c r="F8" t="n">
-        <v>0.130605792017351</v>
+        <v>0.02642253939805492</v>
       </c>
     </row>
     <row r="9">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-4.322937941606254</v>
+        <v>-2.42877999453816</v>
       </c>
       <c r="D9" t="n">
-        <v>3.266078761933942</v>
+        <v>2.915483010011636</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5362691486079537</v>
+        <v>0.3145894935964703</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3290470969534356</v>
+        <v>0.267494655582944</v>
       </c>
     </row>
     <row r="10">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.1651848348566398</v>
+        <v>-3.036876627026079</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4952211373142602</v>
+        <v>1.940810779959529</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1141267743159877</v>
+        <v>0.3000750188263465</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04850560124370749</v>
+        <v>0.1442671860308426</v>
       </c>
     </row>
     <row r="11">
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.5450825208525807</v>
+        <v>-0.9229556616430105</v>
       </c>
       <c r="D11" t="n">
-        <v>0.276093616039488</v>
+        <v>0.3735398899638951</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1264118200633202</v>
+        <v>0.1573277296252271</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02258875887881796</v>
+        <v>0.03056138213933863</v>
       </c>
     </row>
     <row r="12">
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.309894443918188</v>
+        <v>-0.5908062954623317</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4006855448007701</v>
+        <v>0.7621712138471659</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07305510560063784</v>
+        <v>0.168403979479601</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04241688033098397</v>
+        <v>0.0806840316277212</v>
       </c>
     </row>
     <row r="13">
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.01286009652233933</v>
+        <v>-4.23417325537356</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3304894466807287</v>
+        <v>2.571743220910603</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1023900265809088</v>
+        <v>0.4013259746174941</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03340917797683556</v>
+        <v>0.1971863184961042</v>
       </c>
     </row>
   </sheetData>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7377950429239651</v>
+        <v>-10.4646301327313</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08977225334755642</v>
+        <v>8.988662293893295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2253883532731592</v>
+        <v>3.756975406076916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0771671923264181</v>
+        <v>2.945597265739504</v>
       </c>
     </row>
     <row r="3">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.3211105199085166</v>
+        <v>-2.361400993115585</v>
       </c>
       <c r="D3" t="n">
-        <v>2.394088116364138</v>
+        <v>4.393322479802689</v>
       </c>
       <c r="E3" t="n">
-        <v>0.30410553937771</v>
+        <v>0.773758627057917</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5510935284923004</v>
+        <v>1.011295937960688</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +855,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6686696407214151</v>
+        <v>0.7957068851925471</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1170865104144958</v>
+        <v>0.04970498151950814</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0783186314695385</v>
+        <v>0.04829004261850978</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02767647154089171</v>
+        <v>0.01174907768277722</v>
       </c>
     </row>
     <row r="5">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6976072289490973</v>
+        <v>-3.908487148017271</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1850132384046246</v>
+        <v>4.572025659626491</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2601617314874254</v>
+        <v>1.615665179370876</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1591749838601152</v>
+        <v>1.504916369279387</v>
       </c>
     </row>
     <row r="6">
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-6.366257750886285</v>
+        <v>-0.6279745261619515</v>
       </c>
       <c r="D6" t="n">
-        <v>1.932497971041675</v>
+        <v>1.962075428804841</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7195893508100056</v>
+        <v>0.1552006725904082</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1887803831268623</v>
+        <v>0.187051714464807</v>
       </c>
     </row>
     <row r="7">
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-5.013592785498719</v>
+        <v>0.7197192093122093</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8412114680740098</v>
+        <v>0.09333178424804674</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6280036660503108</v>
+        <v>0.02926991739445072</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08784829713577466</v>
+        <v>0.009746702970665004</v>
       </c>
     </row>
     <row r="8">
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-4.425471654466529</v>
+        <v>-1.017234550906559</v>
       </c>
       <c r="D8" t="n">
-        <v>1.077362552155444</v>
+        <v>0.6428137184836439</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4459424333794813</v>
+        <v>0.1658050288748377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08855297912110599</v>
+        <v>0.05283557487473322</v>
       </c>
     </row>
     <row r="9">
@@ -975,16 +975,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-6.647385699492423</v>
+        <v>-4.364490234129791</v>
       </c>
       <c r="D9" t="n">
-        <v>2.222080532128687</v>
+        <v>1.653611623977953</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7704499025036358</v>
+        <v>0.4921903035033937</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2238675799296227</v>
+        <v>0.1517183500315338</v>
       </c>
     </row>
     <row r="10">
@@ -999,16 +999,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.2681276980175969</v>
+        <v>-6.177153104350151</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02558759851581878</v>
+        <v>0.8016335520916439</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07168495721689075</v>
+        <v>0.5335026437243483</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002506237631785042</v>
+        <v>0.05958819787191307</v>
       </c>
     </row>
     <row r="11">
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.8811692724188231</v>
+        <v>-1.676710445959756</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1263734992059499</v>
+        <v>0.2863705114626637</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1539089520231162</v>
+        <v>0.2189966132485675</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01033932092738941</v>
+        <v>0.02342956902164917</v>
       </c>
     </row>
     <row r="12">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6979650750051311</v>
+        <v>0.4244014918746818</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08169540973314657</v>
+        <v>0.1225597620927617</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03197364974984357</v>
+        <v>0.06093330132481885</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008648338986036019</v>
+        <v>0.01297427079548727</v>
       </c>
     </row>
     <row r="13">
@@ -1071,16 +1071,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2940175765971802</v>
+        <v>-8.295180285904481</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05627669922958942</v>
+        <v>0.6056087336139344</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0713677627799358</v>
+        <v>0.7127003837055252</v>
       </c>
       <c r="F13" t="n">
-        <v>0.005689011493085695</v>
+        <v>0.04643455678601387</v>
       </c>
     </row>
   </sheetData>
